--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487992_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487992_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1494</v>
+        <v>5.0006</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5572</v>
+        <v>4.8857</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5923</v>
+        <v>0.1149</v>
       </c>
       <c r="G2" t="n">
         <v>3.1262</v>
@@ -610,13 +610,13 @@
         <v>2.1805</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6801</v>
+        <v>0.5313</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5064</v>
+        <v>-0.1779</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1865</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>0.5502</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GARCIA TEJON</t>
+          <t>J. LOPEZ MUNOZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2886</v>
+        <v>-0.2034</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9846</v>
+        <v>1.571</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2732</v>
+        <v>-1.7744</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.166</v>
+        <v>-2.056</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1156</v>
+        <v>-0.2096</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0503</v>
+        <v>-1.8464</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2928</v>
+        <v>1.1967</v>
       </c>
       <c r="K5" t="n">
-        <v>1.285</v>
+        <v>1.5946</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0078</v>
+        <v>-0.3979</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4588</v>
+        <v>-3.2527</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4007</v>
+        <v>-1.8042</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0581</v>
+        <v>-1.4485</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1982</v>
+        <v>1.9822</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>-0.3964</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7929</v>
+        <v>2.3787</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0756</v>
+        <v>0.7938</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6829</v>
+        <v>0.1672</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3927</v>
+        <v>0.6266</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.9234</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.527</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUNOZ</t>
+          <t>A. SEARA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3272</v>
+        <v>-0.2117</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5876</v>
+        <v>2.2351</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9148</v>
+        <v>-2.4468</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.056</v>
+        <v>-5.3973</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2096</v>
+        <v>-1.2077</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8464</v>
+        <v>-4.1896</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1967</v>
+        <v>-0.8641</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5946</v>
+        <v>1.1979</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3979</v>
+        <v>-2.062</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.2527</v>
+        <v>-4.5332</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8042</v>
+        <v>-2.4056</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4485</v>
+        <v>-2.1276</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9822</v>
+        <v>0.1982</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.3964</v>
+        <v>-2.1805</v>
       </c>
       <c r="R6" t="n">
         <v>2.3787</v>
       </c>
       <c r="S6" t="n">
-        <v>0.67</v>
+        <v>0.2827</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1837</v>
+        <v>-0.3485</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4863</v>
+        <v>0.6312</v>
       </c>
       <c r="V6" t="n">
+        <v>4.7047</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5.6281</v>
+      </c>
+      <c r="X6" t="n">
         <v>-0.9234</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.6036</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-1.527</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SEARA RODRIGUEZ</t>
+          <t>A. GARCIA TEJON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4694</v>
+        <v>-0.8998</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6404</v>
+        <v>0.3734</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1098</v>
+        <v>-1.2732</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.3973</v>
+        <v>-1.166</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2077</v>
+        <v>-0.1156</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.1896</v>
+        <v>-1.0503</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8641</v>
+        <v>1.2928</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1979</v>
+        <v>1.285</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.062</v>
+        <v>0.0078</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.5332</v>
+        <v>-2.4588</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.4056</v>
+        <v>-1.4007</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.1276</v>
+        <v>-1.0581</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1982</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1805</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3787</v>
+        <v>0.7929</v>
       </c>
       <c r="S7" t="n">
-        <v>0.025</v>
+        <v>0.4644</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9432</v>
+        <v>0.0717</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.3927</v>
       </c>
       <c r="V7" t="n">
-        <v>4.7047</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>5.6281</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. CABRERA SALMON</t>
+          <t>A. VALOR LARA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5432</v>
+        <v>-1.3349</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0364</v>
+        <v>1.3988</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5068</v>
+        <v>-2.7337</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.3256</v>
+        <v>-1.1427</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.9754</v>
+        <v>0.0512</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3502</v>
+        <v>-1.1939</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.0572</v>
+        <v>2.2668</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.0974</v>
+        <v>2.2668</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2684</v>
+        <v>-3.4095</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.878</v>
+        <v>-2.2156</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3904</v>
+        <v>-1.1939</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.3964</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.9911</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.5947</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-0.3964</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.9911</v>
-      </c>
       <c r="S8" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.4708</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5471</v>
+        <v>0.1231</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0965</v>
+        <v>0.3478</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5441</v>
+        <v>-0.2666</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.674</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VALOR LARA</t>
+          <t>S. CABRERA SALMON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9243</v>
+        <v>-1.6398</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7251</v>
+        <v>-1.2172</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6495</v>
+        <v>-0.4226</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1427</v>
+        <v>-4.3256</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0512</v>
+        <v>-3.9754</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1939</v>
+        <v>-0.3502</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2668</v>
+        <v>-2.0572</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2668</v>
+        <v>-2.0974</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.4095</v>
+        <v>-2.2684</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.2156</v>
+        <v>-1.878</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1939</v>
+        <v>-0.3904</v>
       </c>
       <c r="P9" t="n">
+        <v>0.5947</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-0.3964</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-0.9911</v>
-      </c>
       <c r="R9" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1186</v>
+        <v>0.547</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5505</v>
+        <v>0.3663</v>
       </c>
       <c r="U9" t="n">
-        <v>0.432</v>
+        <v>0.1807</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2666</v>
+        <v>1.5441</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2666</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4338</v>
+        <v>-2.6</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0156</v>
+        <v>-0.4313</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4494</v>
+        <v>-2.1686</v>
       </c>
       <c r="G10" t="n">
         <v>-2.9106</v>
@@ -1234,13 +1234,13 @@
         <v>1.784</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1931</v>
+        <v>1.027</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2373</v>
+        <v>0.7903</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0441</v>
+        <v>0.2367</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3199</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. CHERNODOLIA SANZ</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4729</v>
+        <v>-3.8479</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2366</v>
+        <v>-0.7634</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2363</v>
+        <v>-3.0845</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.139</v>
+        <v>-3.0229</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.8657</v>
+        <v>-2.5198</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.2733</v>
+        <v>-0.5031</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.4717</v>
+        <v>0.7278</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0487</v>
+        <v>0.1614</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4231</v>
+        <v>0.5664</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.6673</v>
+        <v>-3.7507</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.817</v>
+        <v>-2.6812</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8503</v>
+        <v>-1.0695</v>
       </c>
       <c r="P11" t="n">
-        <v>1.784</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9822</v>
+        <v>0.7929</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9354</v>
+        <v>-0.4285</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4333</v>
+        <v>-0.3018</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5021</v>
+        <v>-0.1267</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0533</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.0533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>V. CHERNODOLIA SANZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6505</v>
+        <v>-4.2878</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3975</v>
+        <v>-2.2761</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.253</v>
+        <v>-2.0117</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.0229</v>
+        <v>-7.139</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.5198</v>
+        <v>-3.8657</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5031</v>
+        <v>-3.2733</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7278</v>
+        <v>-2.4717</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1614</v>
+        <v>-1.0487</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5664</v>
+        <v>-1.4231</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.7507</v>
+        <v>-4.6673</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.6812</v>
+        <v>-2.817</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0695</v>
+        <v>-1.8503</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7929</v>
+        <v>1.9822</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2311</v>
+        <v>1.1206</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9360000000000001</v>
+        <v>0.3939</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2952</v>
+        <v>0.7267</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.0533</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.0533</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.222</v>
+        <v>-9.286199999999997</v>
       </c>
       <c r="E13" t="n">
-        <v>5.442699999999999</v>
+        <v>6.3787</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.6647</v>
+        <v>-15.6648</v>
       </c>
       <c r="G13" t="n">
         <v>-23.2954</v>
@@ -1444,10 +1444,10 @@
         <v>6.026499999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>6.225899999999999</v>
+        <v>6.225900000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1995000000000007</v>
+        <v>-0.1995000000000002</v>
       </c>
       <c r="M13" t="n">
         <v>-29.3219</v>
@@ -1468,13 +1468,13 @@
         <v>13.8757</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8731</v>
+        <v>4.8091</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1482</v>
+        <v>1.0843</v>
       </c>
       <c r="U13" t="n">
-        <v>3.725</v>
+        <v>3.7249</v>
       </c>
       <c r="V13" t="n">
         <v>5.2358</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9924</v>
+        <v>5.5667</v>
       </c>
       <c r="E14" t="n">
         <v>4.1467</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8457</v>
+        <v>1.42</v>
       </c>
       <c r="G14" t="n">
         <v>7.2958</v>
@@ -1546,13 +1546,13 @@
         <v>1.784</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1724</v>
+        <v>-0.2534</v>
       </c>
       <c r="T14" t="n">
         <v>-0.5064</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6788</v>
+        <v>0.253</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2775</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8424</v>
+        <v>4.9587</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2606</v>
+        <v>4.7699</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5819</v>
+        <v>0.1888</v>
       </c>
       <c r="G15" t="n">
         <v>3.3248</v>
@@ -1624,13 +1624,13 @@
         <v>1.784</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3614</v>
+        <v>-0.2451</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1855</v>
+        <v>-0.6762</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8242</v>
+        <v>0.4311</v>
       </c>
       <c r="V15" t="n">
         <v>2.0772</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7589</v>
+        <v>3.1756</v>
       </c>
       <c r="E16" t="n">
         <v>3.6621</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9031</v>
+        <v>-0.4865</v>
       </c>
       <c r="G16" t="n">
         <v>5.5511</v>
@@ -1702,13 +1702,13 @@
         <v>0.5947</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.138</v>
+        <v>-0.7214</v>
       </c>
       <c r="T16" t="n">
         <v>-0.7488</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3892</v>
+        <v>0.0274</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2666</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9277</v>
+        <v>1.0812</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6846</v>
+        <v>1.7865</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7569</v>
+        <v>-0.7053</v>
       </c>
       <c r="G17" t="n">
         <v>0.7623</v>
@@ -1780,13 +1780,13 @@
         <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1627</v>
+        <v>-0.0092</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3192</v>
+        <v>-0.2174</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1565</v>
+        <v>0.2081</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2666</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. YELAMOS MAÑAS</t>
+          <t>M. DIARRA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6027</v>
+        <v>1.0184</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6027</v>
+        <v>1.6496</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0.6312</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6027</v>
+        <v>2.392</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.7416</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6027</v>
+        <v>0.6504</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6027</v>
+        <v>2.5592</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1.7958</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6027</v>
+        <v>0.7634</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-0.1672</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.0542</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.113</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.3092</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.1146</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.4239</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.8811</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1962</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. DIARRA</t>
+          <t>J. YELAMOS MAÑAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5652</v>
+        <v>0.6027</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1403</v>
+        <v>0.6027</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5750999999999999</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>2.392</v>
+        <v>0.6027</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7416</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6504</v>
+        <v>0.6027</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5592</v>
+        <v>0.6027</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7958</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7634</v>
+        <v>0.6027</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1672</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0542</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.113</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.144</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.624</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8811</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1962</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.0772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4599</v>
+        <v>-1.0537</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9945000000000001</v>
+        <v>1.0963</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4544</v>
+        <v>-2.1501</v>
       </c>
       <c r="G20" t="n">
         <v>2.176</v>
@@ -2014,13 +2014,13 @@
         <v>0.5947</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2129</v>
+        <v>-0.8067</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7488</v>
+        <v>-0.6469</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4641</v>
+        <v>-0.1598</v>
       </c>
       <c r="V20" t="n">
         <v>-3.0178</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4893</v>
+        <v>-1.7753</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5258</v>
+        <v>0.7108</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0151</v>
+        <v>-2.4862</v>
       </c>
       <c r="G21" t="n">
         <v>-0.54</v>
@@ -2092,13 +2092,13 @@
         <v>0.5947</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.9599</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3599</v>
+        <v>-0.4551</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0338</v>
+        <v>-0.5049</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8701</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5181</v>
+        <v>-2.6729</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3525</v>
+        <v>-2.7599</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1657</v>
+        <v>0.0871</v>
       </c>
       <c r="G22" t="n">
         <v>1.7308</v>
@@ -2170,13 +2170,13 @@
         <v>1.784</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3528</v>
+        <v>-0.5075</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0479</v>
+        <v>-0.3596</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4007</v>
+        <v>-0.148</v>
       </c>
       <c r="V22" t="n">
         <v>0.2666</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10.222</v>
+        <v>10.9014</v>
       </c>
       <c r="E23" t="n">
-        <v>15.6648</v>
+        <v>15.6647</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.4427</v>
+        <v>-4.7634</v>
       </c>
       <c r="G23" t="n">
         <v>23.2955</v>
@@ -2248,13 +2248,13 @@
         <v>9.911200000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.8733</v>
+        <v>-3.194</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.7249</v>
+        <v>-3.725</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1482999999999998</v>
+        <v>0.5307999999999998</v>
       </c>
       <c r="V23" t="n">
         <v>-5.2359</v>
